--- a/journal_analyzer/live_pure/task_list_live_pure.xlsx
+++ b/journal_analyzer/live_pure/task_list_live_pure.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="12" activeTab="15" autoFilterDateGrouping="1"/>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -657,7 +656,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>45658</v>
+        <v>46023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -672,7 +671,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="5">
@@ -682,7 +681,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -709,10 +708,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -789,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="19.08203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -807,7 +802,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -819,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
@@ -834,8 +828,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4" ht="18.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -848,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -861,24 +853,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -890,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16.25" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -913,10 +887,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -954,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -993,12 +963,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="G8" s="3" t="n"/>
     </row>
@@ -1290,9 +1254,6 @@
     <row r="104">
       <c r="G104" s="3" t="n"/>
     </row>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="손익구분 오류" error="목록에 없는 값입니다. 매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택하세요." promptTitle="손익구분 선택" prompt="매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택" type="list">
@@ -1311,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1329,10 +1290,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1344,7 +1301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1377,14 +1334,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1396,7 +1345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1469,7 +1418,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>계정과목 / 금액열(차변·대변·both) / 실행여부 / 비고</t>
+          <t>계정과목 / 금액열(차변·대변·both) / 실행여부 / 비고 / 관리단위(선택) / 비용구분(선택)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1714,7 +1663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>구분(매출/비용) / 계정과목</t>
+          <t>구분(매출/비용) / 계정과목 / 비용구분(선택)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1804,7 +1753,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>작업명 / 계정과목 / 거래처명 / 금액열 / 실행여부</t>
+          <t>작업명 / 계정과목 / 거래처명 / 금액열 / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1969,7 +1918,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>계정과목 / 구분(차변·대변·both) / 실행여부</t>
+          <t>계정과목 / 구분(차변·대변·both) / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
         </is>
       </c>
     </row>
@@ -2069,6 +2018,33 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>개별 자산이 아닌 계정과목×전표 단위로만 구분됨 — 한 전표에 여러 자산을 묶어 처분하면 한 줄로 잡힘</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>공통-선택</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>관리단위 / 비용구분 열 (2·13·17·25번 시트)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>관리단위(Y) / 비용구분(Y) — 선택 열</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>원장에 '비용구분'(판관/제조 등) 컬럼이 있는 회사 전용 옵션. 계정 행에 Y(또는 O)를 적으면 그 계정의 결과를 비용구분 값별로 나눠서 추출함 (예: 급여 → 급여(판관)·급여(제조)). 관리단위 열도 같은 방식으로 원장의 '전표관리단위'(본사/2공장 등) 컬럼 기준으로 나눔 (13번 시트는 비용구분만 지원).</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>비워두거나 원장에 해당 컬럼이 없으면 무시되고 기존과 동일하게 계정 단위로만 집계됨 — 에러 아님. 열이 없는 task_list는 헤더에 직접 추가해서 사용</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2132,15 +2108,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2152,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="2"/>
@@ -2182,7 +2149,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2895,7 +2861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2935,22 +2901,23 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2992,19 +2959,89 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="3" t="n"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="C3" s="3" t="n"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="C4" s="3" t="n"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>미수금</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="C5" s="3" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="C6" s="3" t="n"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3017,10 +3054,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="15.08203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.4140625" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="8.5" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3051,11 +3089,108 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>미수금</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3127,7 +3262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3145,9 +3280,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3159,7 +3291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -3183,65 +3315,18 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>수익</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/journal_analyzer/live_pure/task_list_live_pure.xlsx
+++ b/journal_analyzer/live_pure/task_list_live_pure.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="13" activeTab="17" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -695,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -705,6 +706,55 @@
       <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>미수금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
         </is>
       </c>
     </row>
@@ -719,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="27.75" customWidth="1" min="1" max="1"/>
@@ -769,6 +819,33 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>리브퓨어(미국본사)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -813,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
@@ -828,7 +905,78 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18.5" customHeight="1"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>미수금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18.5" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>시설장치</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -840,7 +988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -850,6 +998,27 @@
       <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>이자수익</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>이자비용</t>
         </is>
       </c>
     </row>
@@ -963,6 +1132,94 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>급여</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="G8" s="3" t="n"/>
     </row>
@@ -1272,7 +1529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1287,6 +1544,18 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1301,10 +1570,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.9140625" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1331,6 +1601,23 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1885,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>계정과목 / 금액열 / 최소금액 / 실행여부 / 비고</t>
+          <t>계정과목 / 금액열(차변·대변·both) / 최소금액 / 실행여부 / 비고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1683,7 +1970,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정과목 (선택: 개수 / 금액열 열 추가 가능)</t>
+          <t>계정과목 (선택: 개수 / 금액열(차변·대변·both) 열 추가 가능)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1753,7 +2040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>작업명 / 계정과목 / 거래처명 / 금액열 / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
+          <t>작업명 / 계정과목 / 거래처명 / 금액열(차변·대변·both) / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1878,7 +2165,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>계정과목 / 금액유형(차변·대변·차변대변모두) / 실행여부</t>
+          <t>계정과목 / 금액유형(차변·대변·both) / 실행여부</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2108,6 +2395,40 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>리스개량자산</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2119,7 +2440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="2"/>
@@ -2146,6 +2467,23 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>유형자산처분이익</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>유형자산처분손실</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2554,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2416,7 +2754,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2441,7 +2779,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2491,7 +2829,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2591,7 +2929,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2791,7 +3129,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2816,7 +3154,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2841,7 +3179,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3262,10 +3600,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="14.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="17.5" bestFit="1" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3277,6 +3615,18 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>리브퓨어(미국본사)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -3327,6 +3677,54 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>광고선전비</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>행사비</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/journal_analyzer/live_pure/task_list_live_pure.xlsx
+++ b/journal_analyzer/live_pure/task_list_live_pure.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="13" activeTab="17" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="14" activeTab="16" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="15" activeTab="19" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -1093,10 +1093,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.6640625" customWidth="1" style="3" min="3" max="3"/>
     <col width="13" customWidth="1" min="5" max="7"/>
   </cols>
   <sheetData>
@@ -1111,7 +1112,7 @@
           <t>구분</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
@@ -1143,7 +1144,7 @@
           <t>대변</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1157,7 +1158,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>직원급여(판)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1165,7 +1166,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1175,11 +1176,12 @@
           <t>판관비</t>
         </is>
       </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>지급임차료</t>
+          <t>퇴직급여(판)-DB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1187,7 +1189,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1197,11 +1199,12 @@
           <t>판관비</t>
         </is>
       </c>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>퇴직급여(판)-DC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1209,7 +1212,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1219,83 +1222,650 @@
           <t>판관비</t>
         </is>
       </c>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>복리후생비(판)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>여비교통비(판)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>접대비(기업업무추진비)(판)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>통신비(판)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>수도광열비(판)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>세금과공과금(판)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>감가상각비(판)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>지급임차료(판)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>수선비(판)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>보험료(판)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>운반비(판)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>교육훈련비(판)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>도서인쇄비(판)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>소모품비(판)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>지급수수료(판)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>광고선전비(판)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>건물관리비(판)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>판매수수료(판)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>무형고정자산상각(판)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>견본비(판)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>잡비(판)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>창고비(판)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>제품운송비(판)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>소모자재비(판)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>전문직수수료(판)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>조합수수료(판)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>카드수수료(판)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>행사비(판)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
@@ -1493,27 +2063,9 @@
     <row r="98">
       <c r="G98" s="3" t="n"/>
     </row>
-    <row r="99">
-      <c r="G99" s="3" t="n"/>
-    </row>
-    <row r="100">
-      <c r="G100" s="3" t="n"/>
-    </row>
-    <row r="101">
-      <c r="G101" s="3" t="n"/>
-    </row>
-    <row r="102">
-      <c r="G102" s="3" t="n"/>
-    </row>
-    <row r="103">
-      <c r="G103" s="3" t="n"/>
-    </row>
-    <row r="104">
-      <c r="G104" s="3" t="n"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="손익구분 오류" error="목록에 없는 값입니다. 매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택하세요." promptTitle="손익구분 선택" prompt="매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택" type="list">
+    <dataValidation sqref="E2:E494" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="손익구분 오류" error="목록에 없는 값입니다. 매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택하세요." promptTitle="손익구분 선택" prompt="매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택" type="list">
       <formula1>"매출,매출원가,판관비,제조원가,영업외수익,영업외비용"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1607,7 +2159,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>감가상각비(판)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2403,7 +2955,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>감가상각누계액</t>
+          <t>감가상각누계액(비품)</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2420,7 +2972,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>감가상각누계액</t>
+          <t>감가상각누계액(리스개량자산)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">

--- a/journal_analyzer/live_pure/task_list_live_pure.xlsx
+++ b/journal_analyzer/live_pure/task_list_live_pure.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="14" activeTab="16" autoFilterDateGrouping="1"/>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="15" activeTab="19" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="3" activeTab="10" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -93,7 +92,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -103,6 +102,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -239,6 +240,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>감사자동화</author>
+    <author>tc={1816917C-A7C8-4BDA-A2E7-0DF136859404}</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -274,6 +276,14 @@
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Y로 지정하면 이 작업의 월별합산 결과를 비용구분(판관/제조 등)별로도 나눠서 함께 추출 (공란=기존처럼 구분 없이 합산)</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="1" shapeId="0">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    분리, 통합으로 차변대변 분리해서 표시할지 결정</t>
       </text>
     </comment>
   </commentList>
@@ -769,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="27.75" customWidth="1" min="1" max="1"/>
@@ -814,6 +824,11 @@
           <t>비용구분</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>표시방식</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -840,10 +855,209 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>리브퓨어(태국지사)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>상품매입</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티 주식회사</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>상품매입</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>리브퓨어(미국본사)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티 주식회사</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>리브퓨어(미국본사)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>매출채권</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>리브퓨어(미국본사)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(주)콘코디아테크널러지</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -890,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
@@ -929,7 +1143,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18.5" customHeight="1">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>자산</t>
@@ -937,31 +1151,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.5" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>비품</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>시설장치</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>부채</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>외상매입금</t>
+          <t>시설장치</t>
         </is>
       </c>
     </row>
@@ -972,6 +1186,18 @@
         </is>
       </c>
       <c r="B7" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>미지급금</t>
         </is>
@@ -1033,10 +1259,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16.25" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1053,6 +1280,55 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>표시방식(분리/통합)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>퇴직급여충당부채</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>퇴직연금운용자산</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>분리</t>
         </is>
       </c>
     </row>
@@ -2081,21 +2357,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>샘플링비율</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>최소건수</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>최대건수</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>금액상위</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>최신</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>이상치</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>월별</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>랜덤</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>중점검토사항</t>
         </is>
       </c>
     </row>
@@ -2109,6 +2440,30 @@
         <is>
           <t>Y</t>
         </is>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2772,12 +3127,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>계정과목 / 실행여부</t>
+          <t>계정과목 / 실행여부 / 샘플링비율 / 최소건수 / 최대건수 / 금액상위 / 최신 / 이상치 / 월별 / 랜덤 / 중점검토사항(선택)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>.env에 GEMINI_API_KEY 필요 (Gemini 실제 호출, 비용 발생)</t>
+          <t>.env에 GEMINI_API_KEY 필요 (Gemini 실제 호출, 계정 1행당 1회 호출·비용 발생). 샘플크기 = 당기 거래건수 × 샘플링비율(최소~최대건수로 제한). 구성비(금액상위/최신/이상치/월별/랜덤)는 합계 100% 기준이며 합이 달라도 비율대로 자동 환산. 이상치 = 주말전기·금액이상치(IQR)·라운드금액(100만원 단위)·1회성거래처·적요미기재. 빈 칸은 기본값(5%, 30~150건, 30/20/10/30/10%). 중점검토사항에 적은 내용은 AI 분석 지시에 추가됨. 분석목록 26번 분석대상을 "전체"로 두면 전기 동기간 비교가 들어감(샘플은 당기에서만 추출)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>결과 시트 하나로 출력: 샘플링 / 계정요약 / 거래특징 / 경영자주장별 위험요소 / 감사인 제언 / 종합결론 / 확인필요전표 / 샘플내역 / 가명대조. AI에는 거래처·적요 속 실명은 가명, 직함 앞 사람이름·계좌번호는 마스킹해서 전송</t>
         </is>
       </c>
     </row>
@@ -3114,6 +3474,9 @@
           <t>전체</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3626,7 +3989,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>각 계정별로 계정과목 차변/대변/차변대변모두 를 선택하여 데이터추출</t>
+          <t>각 계정별로 계정과목 차변/대변/both 를 선택하여 데이터추출</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3701,7 +4064,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립 실행)</t>
+          <t>계정별 스마트샘플(비율·구성 지정) + 통계를 Gemini로 분석 — 계정요약/거래특징/경영자주장별 위험/감사인 제언</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3711,7 +4074,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전체</t>
         </is>
       </c>
     </row>
@@ -3751,7 +4114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3803,6 +4166,57 @@
         </is>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>직원급여</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/journal_analyzer/live_pure/task_list_live_pure.xlsx
+++ b/journal_analyzer/live_pure/task_list_live_pure.xlsx
@@ -16,17 +16,18 @@
     <sheet name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="17_거래처분석" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="21_총계정원장" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="22_은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="23_계정별 상세거래내역" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="24_리스완전성" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="25_손익월별분석" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="26_AI계정별분석_실행" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="27_감가상각_평가손익분석" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="유형자산_처분손익" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="15_감사샘플링" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="17_거래처분석" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="23_계정별 상세거래내역" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="24_리스완전성" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="25_손익월별분석" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="26_AI계정별분석_실행" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="27_감가상각_평가손익분석" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -35,9 +36,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -92,7 +94,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +106,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -779,6 +783,490 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>종료일</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>샘플링방법</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>금액타입</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>샘플크기</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>통계표사용</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>신뢰수준</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>허용왜곡표시</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>예상왜곡표시</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>이상거래포함</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>개별유의금액</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>예시) 매출 실재성 — 차변 MUS 30건</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>체계적</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>예시) 출금 증빙 — 대변 체계적 40건</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>예시) 통계표로 크기 계산 + 1천만원 이상 전수</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"MUS,체계적,무작위,금액상위"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"차변,대변,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B200 H2:H200 L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
@@ -1069,7 +1557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1098,7 +1586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1208,7 +1696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1253,7 +1741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1337,7 +1825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1363,7 +1851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2351,7 +2839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2471,68 +2959,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10.9140625" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>그룹기준열</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>감가상각비(판)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2897,17 +3323,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI계정별분석 (시트 미생성)</t>
+          <t>감사샘플링</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>계정과목 / 실행여부</t>
+          <t>계정과목 / 실행여부 / 시작일·종료일(선택) / 샘플링방법(MUS·체계적·무작위·금액상위) / 금액타입(차변·대변·both) / 샘플크기 / 통계표사용(Y/N) / 신뢰수준 / 허용왜곡표시 / 예상왜곡표시 / 이상거래포함(Y/N) / 개별유의금액(선택)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>쓰려면 시트명을 정확히 'AI계정별분석'으로 새로 만들고 계정과목 입력. Gemini 호출 없이 월별추이·샘플만 추출(26번과 형식은 같으나 AI 분석은 안 함)</t>
+          <t>계정 1줄 = 샘플링 1건, 샘플은 해당 계정의 전표 줄 단위(같은 전표의 상대계정 줄은 뽑지 않고 상대계정 열에 참고 표시). MUS=금액 누적 기준 구간마다 1건(구간보다 큰 줄은 반드시 선택) / 체계적=건수 기준 일정 간격 / 무작위 / 금액상위. 통계표사용=Y면 샘플크기 = 모집단금액×신뢰계수÷(허용왜곡표시−예상왜곡표시×확장계수) (95%: 3.0·1.6, 90%: 2.31·1.5). 이상거래포함=Y면 Z-score 3 이상·최대값을 샘플크기 안에서 우선 포함. 개별유의금액 이상은 샘플크기와 별도로 전수 포함. 시드 고정(42)이라 다시 돌려도 같은 샘플</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>결과: 샘플링조건(모집단·원장대사·크기근거·커버리지) + 계정별 샘플 시트(증빙종류·증빙확인·승인확인·예외사항·확인자 빈칸). AI로 보내지 않으므로 거래처·적요 실명 출력</t>
         </is>
       </c>
     </row>
@@ -3253,6 +3684,68 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.9140625" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>그룹기준열</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>감가상각비(판)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3346,7 +3839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3784,12 +4277,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI 계정별 분석</t>
+          <t>감사샘플링</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
+          <t>계정별 감사증빙 샘플 추출 (MUS/체계적/무작위/금액상위, 전표 줄 단위) → 15_감사샘플링 시트 참조</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">

--- a/journal_analyzer/live_pure/task_list_live_pure.xlsx
+++ b/journal_analyzer/live_pure/task_list_live_pure.xlsx
@@ -41,7 +41,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -70,13 +70,30 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00305496"/>
+    </font>
+    <font>
+      <color rgb="00404040"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -94,7 +111,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +125,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1130,94 +1150,209 @@
       <c r="D30" s="9" t="n"/>
     </row>
     <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>■ 15번 감사샘플링 작성 안내 (이 안내 행들은 실행여부가 비어 있어 분석에 읽히지 않음 — 지우지 말고 위쪽 행에 계정 입력)</t>
+        </is>
+      </c>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
     </row>
     <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>[기본 항목]</t>
+        </is>
+      </c>
       <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
     </row>
     <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>· 실행여부: Y(또는 O)인 행만 실행.  · 시작일/종료일: 비우면 분개장 전체 기간.</t>
+        </is>
+      </c>
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="9" t="n"/>
     </row>
     <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>· 샘플링방법: MUS / 체계적 / 무작위 / 금액상위 (빈칸 = MUS).</t>
+        </is>
+      </c>
       <c r="C34" s="9" t="n"/>
       <c r="D34" s="9" t="n"/>
     </row>
     <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>· 금액타입: 차변 / 대변 / both (빈칸·그 외 값 = both). 결과시트명은 계정명_차 / _대 / _양.</t>
+        </is>
+      </c>
       <c r="C35" s="9" t="n"/>
       <c r="D35" s="9" t="n"/>
     </row>
     <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>[샘플크기 — 통계표사용에 따라 결정]</t>
+        </is>
+      </c>
       <c r="C36" s="9" t="n"/>
       <c r="D36" s="9" t="n"/>
     </row>
     <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>· 통계표사용 = N(또는 빈칸): 샘플크기 칸의 입력값대로 추출 (빈칸 = 30건). 신뢰수준·허용/예상왜곡표시는 무시됨.</t>
+        </is>
+      </c>
       <c r="C37" s="9" t="n"/>
       <c r="D37" s="9" t="n"/>
     </row>
     <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>· 통계표사용 = Y: 샘플크기 = 모집단금액 × 신뢰계수 ÷ (허용왜곡표시 − 예상왜곡표시 × 확장계수) 로 자동 계산, 샘플크기 칸 입력값은 무시됨.</t>
+        </is>
+      </c>
       <c r="C38" s="9" t="n"/>
       <c r="D38" s="9" t="n"/>
     </row>
     <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 신뢰계수/확장계수: 90% = 2.31/1.5, 95% = 3.00/1.6, 99% = 4.61/1.9 (모집단금액은 개별유의금액 전수분을 뺀 금액).</t>
+        </is>
+      </c>
       <c r="C39" s="9" t="n"/>
       <c r="D39" s="9" t="n"/>
     </row>
     <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>· 신뢰수준: 0.95 또는 95 둘 다 가능 (빈칸 = 0.95). 90/95/99% 중 가까운 값 적용.</t>
+        </is>
+      </c>
       <c r="C40" s="9" t="n"/>
       <c r="D40" s="9" t="n"/>
     </row>
     <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>· 허용왜곡표시: 통계표사용 = Y이면 필수(예: 수행중요성). 비우면 해당 계정은 샘플 미추출 → 샘플링조건 시트 결과시트 "미추출" + 비고에 사유 표시.</t>
+        </is>
+      </c>
       <c r="C41" s="9" t="n"/>
       <c r="D41" s="9" t="n"/>
     </row>
     <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>· 예상왜곡표시: 비워도 됨(빈칸 = 0). 0이면 샘플크기가 가장 작게 나오고, 전기 왜곡표시 등 오류 위험이 있으면 금액을 넣어 보수적으로(샘플 증가).</t>
+        </is>
+      </c>
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="9" t="n"/>
     </row>
     <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 예상왜곡표시 × 확장계수 ≥ 허용왜곡표시 이면 계산 불가 → 해당 계정 건너뛰고 비고에 사유 표시.</t>
+        </is>
+      </c>
       <c r="C43" s="9" t="n"/>
       <c r="D43" s="9" t="n"/>
     </row>
     <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>[금액 입력 형식 — 허용왜곡표시·예상왜곡표시·개별유의금액]</t>
+        </is>
+      </c>
       <c r="C44" s="9" t="n"/>
       <c r="D44" s="9" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>· 원 단위 숫자로 입력: 500000000 또는 500,000,000 (엑셀 숫자 셀 OK).</t>
+        </is>
+      </c>
       <c r="C45" s="9" t="n"/>
       <c r="D45" s="9" t="n"/>
     </row>
     <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>· "5억", "500,000,000원"처럼 글자가 섞이면 빈칸으로 처리됨. "5%", 0.05 같은 비율 입력 금지(5원·0.05원으로 읽힘).</t>
+        </is>
+      </c>
       <c r="C46" s="9" t="n"/>
       <c r="D46" s="9" t="n"/>
     </row>
     <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>[추가 옵션]</t>
+        </is>
+      </c>
       <c r="C47" s="9" t="n"/>
       <c r="D47" s="9" t="n"/>
     </row>
     <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>· 개별유의금액: 이 금액 이상인 줄은 전수 추출(샘플크기와 별도로 추가). 빈칸 = 전수 없음.</t>
+        </is>
+      </c>
       <c r="C48" s="9" t="n"/>
       <c r="D48" s="9" t="n"/>
     </row>
     <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>· 이상거래포함 = Y: 최대값 + Z-score 3 이상 거래를 샘플크기의 20%까지 먼저 포함(샘플크기 안에 포함됨).</t>
+        </is>
+      </c>
       <c r="C49" s="9" t="n"/>
       <c r="D49" s="9" t="n"/>
     </row>
     <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>[결과 확인]</t>
+        </is>
+      </c>
       <c r="C50" s="9" t="n"/>
       <c r="D50" s="9" t="n"/>
     </row>
     <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>· 샘플링조건 시트: 계정별 모집단·원장 대사·샘플크기 근거·추출조건 요약. 샘플 시트가 안 나오면 이 시트의 결과시트·비고 열부터 확인.</t>
+        </is>
+      </c>
       <c r="C51" s="9" t="n"/>
       <c r="D51" s="9" t="n"/>
     </row>
     <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>· 샘플 단위는 해당 계정의 전표 "줄". 같은 전표의 상대계정 줄은 뽑지 않고 상대계정 열에 참고로만 표시.</t>
+        </is>
+      </c>
       <c r="C52" s="9" t="n"/>
       <c r="D52" s="9" t="n"/>
     </row>
     <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>· 시드 42 고정 → 같은 조건으로 재실행하면 같은 샘플(조서 재현성). 증빙종류~확인자 열은 감사인이 직접 기재.</t>
+        </is>
+      </c>
       <c r="C53" s="9" t="n"/>
       <c r="D53" s="9" t="n"/>
     </row>

--- a/journal_analyzer/live_pure/task_list_live_pure.xlsx
+++ b/journal_analyzer/live_pure/task_list_live_pure.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="3" activeTab="10" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="10" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="분석목록" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="02_거래처 전기_당기 비교" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="03_벤포드 분석" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="08_상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="10_라운드넘버 분석" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="15_감사샘플링" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="17_거래처분석" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="23_계정별 상세거래내역" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="24_리스완전성" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="25_손익월별분석" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="26_AI계정별분석_실행" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="27_감가상각_평가손익분석" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석목록" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_거래처 전기_당기 비교" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_벤포드 분석" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_라운드넘버 분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_감사샘플링" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_거래처분석" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_계정별 상세거래내역" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_리스완전성" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_손익월별분석" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_AI계정별분석_실행" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_감가상각_평가손익분석" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -39,7 +39,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -71,16 +71,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00305496"/>
+      <color rgb="FF305496"/>
+      <sz val="11"/>
     </font>
     <font>
-      <color rgb="00404040"/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF404040"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -92,7 +103,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,15 +122,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +137,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -264,7 +276,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>감사자동화</author>
-    <author>tc={1816917C-A7C8-4BDA-A2E7-0DF136859404}</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -284,30 +295,27 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>차변/대변/both 중 하나 — 상세내역·월별합산에 포함할 금액 방향. 공란이면 자동으로 both(차변+대변 모두) 처리됨</t>
+        <t>원장 적요에 포함된 문구(부분일치), 콤마(,)로 여러 개 지정 가능(OR). 기재하면 계정과목·거래처명·금액열 조건에 더해 적요 조건까지 만족하는 거래만 추출. 공란이면 적요 조건 없이 기존처럼 추출. 거래처명을 비우고 적요만 적으면 적요 기준으로 추출(거래처별 시트는 적요 문구별로 생성)</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Y(또는 O)로 표시한 행만 분석에 포함됨</t>
+        <t>차변/대변/both 중 하나 — 상세내역·월별합산에 포함할 금액 방향. 공란이면 자동으로 both(차변+대변 모두) 처리됨</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Y로 지정하면 이 작업의 월별합산 결과를 전표관리단위(본사/2공장 등)별로도 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>
+        <t>Y(또는 O)로 표시한 행만 분석에 포함됨</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Y로 지정하면 이 작업의 월별합산 결과를 비용구분(판관/제조 등)별로도 나눠서 함께 추출 (공란=기존처럼 구분 없이 합산)</t>
+        <t>Y로 지정하면 이 작업의 월별합산 결과를 전표관리단위(본사/2공장 등)별로도 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="1" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    분리, 통합으로 차변대변 분리해서 표시할지 결정</t>
+        <t>Y로 지정하면 이 작업의 월별합산 결과를 비용구분(판관/제조 등)별로도 나눠서 함께 추출 (공란=기존처럼 구분 없이 합산)</t>
       </text>
     </comment>
   </commentList>
@@ -690,7 +698,7 @@
           <t>StartDate</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="12" t="n">
         <v>46023</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -705,7 +713,7 @@
           <t>EndDate</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="12" t="n">
         <v>46387</v>
       </c>
     </row>
@@ -804,15 +812,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N59"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
@@ -823,72 +829,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>시작일</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>종료일</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>샘플링방법</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>금액타입</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>샘플크기</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>통계표사용</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>신뢰수준</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>허용왜곡표시</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>예상왜곡표시</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>이상거래포함</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>개별유의금액</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -905,8 +911,8 @@
           <t>N</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>MUS</t>
@@ -925,11 +931,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="I2" s="6" t="n">
         <v>0.95</v>
       </c>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n">
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -937,7 +943,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M2" s="10" t="n"/>
+      <c r="M2" s="8" t="n"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>예시) 매출 실재성 — 차변 MUS 30건</t>
@@ -955,8 +961,8 @@
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>체계적</t>
@@ -975,11 +981,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="6" t="n">
         <v>0.95</v>
       </c>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n">
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -987,7 +993,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M3" s="10" t="n"/>
+      <c r="M3" s="8" t="n"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>예시) 출금 증빙 — 대변 체계적 40건</t>
@@ -1005,8 +1011,8 @@
           <t>N</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>MUS</t>
@@ -1022,13 +1028,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="6" t="n">
         <v>0.95</v>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="J4" s="8" t="n">
         <v>50000000</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -1036,7 +1042,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="8" t="n">
         <v>10000000</v>
       </c>
       <c r="N4" t="inlineStr">
@@ -1046,339 +1052,344 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>상품매출</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
     </row>
     <row r="13">
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
     </row>
     <row r="15">
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
     </row>
     <row r="17">
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
     </row>
     <row r="25">
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>■ 15번 감사샘플링 작성 안내 (이 안내 행들은 실행여부가 비어 있어 분석에 읽히지 않음 — 지우지 말고 위쪽 행에 계정 입력)</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>[기본 항목]</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>· 실행여부: Y(또는 O)인 행만 실행.  · 시작일/종료일: 비우면 분개장 전체 기간.</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>· 샘플링방법: MUS / 체계적 / 무작위 / 금액상위 (빈칸 = MUS).</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>· 금액타입: 차변 / 대변 / both (빈칸·그 외 값 = both). 결과시트명은 계정명_차 / _대 / _양.</t>
         </is>
       </c>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>[샘플크기 — 통계표사용에 따라 결정]</t>
         </is>
       </c>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>· 통계표사용 = N(또는 빈칸): 샘플크기 칸의 입력값대로 추출 (빈칸 = 30건). 신뢰수준·허용/예상왜곡표시는 무시됨.</t>
         </is>
       </c>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>· 통계표사용 = Y: 샘플크기 = 모집단금액 × 신뢰계수 ÷ (허용왜곡표시 − 예상왜곡표시 × 확장계수) 로 자동 계산, 샘플크기 칸 입력값은 무시됨.</t>
         </is>
       </c>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    - 신뢰계수/확장계수: 90% = 2.31/1.5, 95% = 3.00/1.6, 99% = 4.61/1.9 (모집단금액은 개별유의금액 전수분을 뺀 금액).</t>
         </is>
       </c>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>· 신뢰수준: 0.95 또는 95 둘 다 가능 (빈칸 = 0.95). 90/95/99% 중 가까운 값 적용.</t>
         </is>
       </c>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="9" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>· 허용왜곡표시: 통계표사용 = Y이면 필수(예: 수행중요성). 비우면 해당 계정은 샘플 미추출 → 샘플링조건 시트 결과시트 "미추출" + 비고에 사유 표시.</t>
         </is>
       </c>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>· 예상왜곡표시: 비워도 됨(빈칸 = 0). 0이면 샘플크기가 가장 작게 나오고, 전기 왜곡표시 등 오류 위험이 있으면 금액을 넣어 보수적으로(샘플 증가).</t>
         </is>
       </c>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    - 예상왜곡표시 × 확장계수 ≥ 허용왜곡표시 이면 계산 불가 → 해당 계정 건너뛰고 비고에 사유 표시.</t>
         </is>
       </c>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>[금액 입력 형식 — 허용왜곡표시·예상왜곡표시·개별유의금액]</t>
         </is>
       </c>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>· 원 단위 숫자로 입력: 500000000 또는 500,000,000 (엑셀 숫자 셀 OK).</t>
         </is>
       </c>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>· "5억", "500,000,000원"처럼 글자가 섞이면 빈칸으로 처리됨. "5%", 0.05 같은 비율 입력 금지(5원·0.05원으로 읽힘).</t>
         </is>
       </c>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>[추가 옵션]</t>
         </is>
       </c>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>· 개별유의금액: 이 금액 이상인 줄은 전수 추출(샘플크기와 별도로 추가). 빈칸 = 전수 없음.</t>
         </is>
       </c>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="9" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>· 이상거래포함 = Y: 최대값 + Z-score 3 이상 거래를 샘플크기의 20%까지 먼저 포함(샘플크기 안에 포함됨).</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="9" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>[결과 확인]</t>
         </is>
       </c>
-      <c r="C50" s="9" t="n"/>
-      <c r="D50" s="9" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="14" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>· 샘플링조건 시트: 계정별 모집단·원장 대사·샘플크기 근거·추출조건 요약. 샘플 시트가 안 나오면 이 시트의 결과시트·비고 열부터 확인.</t>
         </is>
       </c>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="14" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>· 샘플 단위는 해당 계정의 전표 "줄". 같은 전표의 상대계정 줄은 뽑지 않고 상대계정 열에 참고로만 표시.</t>
         </is>
       </c>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
+      <c r="C52" s="14" t="n"/>
+      <c r="D52" s="14" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>· 시드 42 고정 → 같은 조건으로 재실행하면 같은 샘플(조서 재현성). 증빙종류~확인자 열은 감사인이 직접 기재.</t>
         </is>
       </c>
-      <c r="C53" s="9" t="n"/>
-      <c r="D53" s="9" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="14" t="n"/>
     </row>
     <row r="54">
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="9" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="14" t="n"/>
     </row>
     <row r="55">
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="14" t="n"/>
     </row>
     <row r="56">
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="14" t="n"/>
     </row>
     <row r="57">
-      <c r="C57" s="9" t="n"/>
-      <c r="D57" s="9" t="n"/>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="14" t="n"/>
     </row>
     <row r="58">
-      <c r="C58" s="9" t="n"/>
-      <c r="D58" s="9" t="n"/>
+      <c r="C58" s="14" t="n"/>
+      <c r="D58" s="14" t="n"/>
     </row>
     <row r="59">
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
+      <c r="C59" s="14" t="n"/>
+      <c r="D59" s="14" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1402,13 +1413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="27.75" customWidth="1" min="1" max="1"/>
-    <col width="26.9140625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="35.25" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="5" max="7"/>
+    <col width="26.9140625" customWidth="1" min="2" max="2"/>
+    <col width="35.25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1429,25 +1441,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>적요</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>금액열</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>관리단위</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>비용구분</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>표시방식</t>
         </is>
@@ -1456,7 +1473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
+          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명·적요는 콤마로 여러 개 가능 / 적요 기재 시 적요 조건도 추가(공란=조건 없음) / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1493,12 @@
           <t>리브퓨어(미국본사)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1503,12 +1520,12 @@
           <t>리브퓨어(태국지사)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1530,12 +1547,12 @@
           <t>코스맥스엔비티 주식회사</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1557,12 +1574,12 @@
           <t>리브퓨어(미국본사)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1584,17 +1601,17 @@
           <t>코스맥스엔비티 주식회사</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>분리</t>
         </is>
@@ -1616,17 +1633,17 @@
           <t>리브퓨어(미국본사)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>분리</t>
         </is>
@@ -1648,12 +1665,12 @@
           <t>리브퓨어(미국본사)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1675,12 +1692,12 @@
           <t>(주)콘코디아테크널러지</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1882,7 +1899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16.25" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1950,6 +1967,50 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>잡이익</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>제품운송비</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>분리</t>
         </is>
@@ -2986,68 +3047,65 @@
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="4" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="9" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>샘플링비율</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>최소건수</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>최대건수</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>금액상위</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>최신</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>이상치</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>월별</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>랜덤</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>중점검토사항</t>
         </is>
@@ -3064,7 +3122,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="D2" t="n">
@@ -3073,19 +3131,19 @@
       <c r="E2" t="n">
         <v>150</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="H2" s="8" t="n">
+      <c r="H2" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="I2" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="J2" s="8" t="n">
+      <c r="J2" s="6" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5169,19 +5227,19 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="6" t="n"/>
+      <c r="C2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="C3" s="6" t="n"/>
+      <c r="C3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="C5" s="6" t="n"/>
+      <c r="C5" s="13" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
